--- a/testakten/versausgleich-haerte-bgh-schaefer-nuernberg/xlsx/liquiditaetsbetrachtung_immobilien_schaefer.xlsx
+++ b/testakten/versausgleich-haerte-bgh-schaefer-nuernberg/xlsx/liquiditaetsbetrachtung_immobilien_schaefer.xlsx
@@ -504,17 +504,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Liquiditaetsbetrachtung Immobilien Frau L. Schaefer (Erbschaft Winterstein 2019)</t>
+          <t>Liquiditätsbetrachtung Immobilien Frau L. Schäfer (Erbschaft Winterstein 2019)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stichtag 31.12.2021; Werte aus SV-Gutachten Weisbacher 18.10.2022 sowie Hausverwaltung Pirsch und Maerz</t>
-        </is>
-      </c>
-    </row>
+          <t>Stichtag 31.12.2021; Werte aus SV-Gutachten Weisbacher 18.10.2022 sowie Hausverwaltung Pirsch und März</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -609,7 +610,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>ETW Muenchen Hohenzollernstr. 47</t>
+          <t>ETW München Hohenzollernstr. 47</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
@@ -655,10 +656,11 @@
         <v>3150000</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Zusatzposten Vermoegen</t>
+          <t>Zusatzposten Vermögen</t>
         </is>
       </c>
     </row>
@@ -682,10 +684,11 @@
         <v>450000</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Gesamt-Vermoegen</t>
+          <t>Gesamt-Vermögen</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
@@ -724,6 +727,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -792,7 +796,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>ETW Muenchen</t>
+          <t>ETW München</t>
         </is>
       </c>
       <c r="B6" s="11" t="n">
